--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线3层（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="483">
   <si>
     <t>ID</t>
   </si>
@@ -84,6 +84,9 @@
     <t/>
   </si>
   <si>
+    <t>22 the_mountain-horror</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
@@ -261,10 +264,81 @@
     <t>“哒哒哒......”</t>
   </si>
   <si>
+    <t>18 enhanced_APPLE</t>
+  </si>
+  <si>
     <t>parallel(charfadeout(L,1);playsfx(FootStep))</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=17</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=17</t>
+    </r>
+  </si>
+  <si>
+    <t>就在故事迎来至关重要的转折之际，走廊深处突然传来了由远及近的脚步声，像某种死亡的鼓点，一步一步地踩在你们的心跳上。索菲亚的身体骤然绷紧，先前松弛下来的肩背再次绷成了一道紧绷的直线。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=97</t>
+    </r>
   </si>
   <si>
     <t>22</t>
@@ -676,6 +750,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -736,6 +815,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -771,6 +855,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -2206,10 +2295,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2745,7 +2834,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2796,7 +2885,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" ht="30" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2822,24 +2911,24 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" ht="90" spans="1:12">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -2854,7 +2943,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -2869,12 +2958,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" ht="42" spans="1:12">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2892,7 +2981,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2907,12 +2996,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="40.5" spans="1:12">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2930,7 +3019,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2945,20 +3034,19 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="42" spans="1:12">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="D6"/>
       <c r="E6" t="s">
         <v>15</v>
       </c>
@@ -2966,7 +3054,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2977,14 +3065,13 @@
       <c r="J6" t="s">
         <v>15</v>
       </c>
-      <c r="K6"/>
       <c r="L6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:12">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -2992,7 +3079,6 @@
       <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="D7"/>
       <c r="E7" t="s">
         <v>15</v>
       </c>
@@ -3000,7 +3086,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3011,14 +3097,13 @@
       <c r="J7" t="s">
         <v>15</v>
       </c>
-      <c r="K7"/>
       <c r="L7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:12">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -3036,7 +3121,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3051,21 +3136,21 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:12">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -3074,7 +3159,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3086,24 +3171,24 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" ht="54" spans="1:12">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3112,7 +3197,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3127,21 +3212,21 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:12">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3150,7 +3235,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3162,15 +3247,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3188,7 +3273,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3203,21 +3288,21 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="55.5" spans="1:12">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3226,7 +3311,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3238,15 +3323,15 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="40.5" spans="1:12">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3255,7 +3340,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3264,7 +3349,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3276,15 +3361,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" ht="54" spans="1:12">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3302,7 +3387,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3317,21 +3402,21 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="40.5" spans="1:12">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3340,7 +3425,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3352,24 +3437,24 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" ht="72" spans="1:12">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3378,7 +3463,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3393,21 +3478,21 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" ht="30" spans="1:12">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3416,7 +3501,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3431,12 +3516,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:12">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3445,7 +3530,7 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3454,74 +3539,53 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>75</v>
-      </c>
-      <c r="L19" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="20" ht="30" spans="1:12">
-      <c r="A20" t="s">
         <v>77</v>
       </c>
+      <c r="L19" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" ht="67.5" spans="1:12">
+      <c r="A20">
+        <v>97</v>
+      </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
-      <c r="D20" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
       <c r="G20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>15</v>
-      </c>
-      <c r="K20" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" t="s">
         <v>79</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:12">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3530,7 +3594,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3542,24 +3606,24 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" ht="54" spans="1:12">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" ht="30" spans="1:12">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3568,7 +3632,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3580,24 +3644,24 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L22" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" ht="30" spans="1:12">
+    <row r="23" ht="54" spans="1:12">
       <c r="A23" t="s">
         <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -3618,62 +3682,62 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="L23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" ht="54" spans="1:12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="1:12">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" ht="54" spans="1:12">
+      <c r="A25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" t="s">
         <v>13</v>
       </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" t="s">
-        <v>15</v>
-      </c>
-      <c r="I24" t="s">
-        <v>15</v>
-      </c>
-      <c r="J24" t="s">
-        <v>15</v>
-      </c>
-      <c r="K24" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="25" ht="30" spans="1:12">
-      <c r="A25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" t="s">
-        <v>39</v>
-      </c>
       <c r="C25" t="s">
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3682,7 +3746,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3697,21 +3761,21 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:12">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3720,7 +3784,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3732,62 +3796,62 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" ht="40.5" spans="1:12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" ht="30" spans="1:12">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K27" t="s">
+        <v>50</v>
+      </c>
+      <c r="L27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" ht="40.5" spans="1:12">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
         <v>13</v>
       </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G27" t="s">
-        <v>100</v>
-      </c>
-      <c r="H27" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" t="s">
-        <v>15</v>
-      </c>
-      <c r="K27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" ht="30" spans="1:12">
-      <c r="A28" t="s">
-        <v>102</v>
-      </c>
-      <c r="B28" t="s">
-        <v>39</v>
-      </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E28" t="s">
         <v>15</v>
@@ -3796,7 +3860,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3808,62 +3872,62 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:12">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s">
+        <v>107</v>
+      </c>
+      <c r="H29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" t="s">
+        <v>15</v>
+      </c>
+      <c r="K29" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" ht="30" spans="1:12">
+      <c r="A30" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" t="s">
         <v>40</v>
       </c>
-      <c r="E29" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" t="s">
-        <v>15</v>
-      </c>
-      <c r="G29" t="s">
-        <v>106</v>
-      </c>
-      <c r="H29" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" t="s">
-        <v>15</v>
-      </c>
-      <c r="J29" t="s">
-        <v>15</v>
-      </c>
-      <c r="K29" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" ht="55.5" spans="1:12">
-      <c r="A30" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3872,7 +3936,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3884,15 +3948,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="31" ht="27" spans="1:12">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" ht="55.5" spans="1:12">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3901,7 +3965,7 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3910,7 +3974,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3922,15 +3986,15 @@
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" ht="40.5" spans="1:12">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3948,7 +4012,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3963,12 +4027,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="33" ht="27" spans="1:12">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3986,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4001,12 +4065,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="34" ht="45" spans="1:12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" ht="27" spans="1:12">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4024,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4036,15 +4100,15 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" ht="45" spans="1:12">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4074,15 +4138,15 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="L35" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="36" ht="40.5" spans="1:12">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4100,7 +4164,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4115,12 +4179,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" ht="40.5" spans="1:12">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4138,7 +4202,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4153,12 +4217,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4176,7 +4240,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4188,7 +4252,7 @@
         <v>15</v>
       </c>
       <c r="K38" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="L38" t="s">
         <v>134</v>
@@ -4226,15 +4290,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="L39" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="40" ht="55.5" spans="1:12">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4252,7 +4316,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4267,12 +4331,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="41" ht="40.5" spans="1:12">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" ht="55.5" spans="1:12">
       <c r="A41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4290,7 +4354,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4305,12 +4369,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" ht="40.5" spans="1:12">
       <c r="A42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4328,7 +4392,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4343,12 +4407,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="43" ht="55.5" spans="1:12">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4366,7 +4430,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4381,12 +4445,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" ht="55.5" spans="1:12">
       <c r="A44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4404,7 +4468,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4419,15 +4483,15 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" ht="55.5" spans="1:12">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B45" t="s">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -4454,18 +4518,18 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
+        <v>15</v>
+      </c>
+      <c r="L45" t="s">
         <v>156</v>
       </c>
-      <c r="L45" t="s">
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="46" ht="54" spans="1:12">
-      <c r="A46" t="s">
+      <c r="B46" t="s">
         <v>158</v>
-      </c>
-      <c r="B46" t="s">
-        <v>13</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -4498,7 +4562,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="47" ht="40.5" spans="1:12">
+    <row r="47" ht="54" spans="1:12">
       <c r="A47" t="s">
         <v>162</v>
       </c>
@@ -4530,15 +4594,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="L47" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="48" ht="67.5" spans="1:12">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4556,7 +4620,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4571,12 +4635,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="49" ht="54" spans="1:12">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="49" ht="67.5" spans="1:12">
       <c r="A49" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4594,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4609,15 +4673,15 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -4632,7 +4696,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4647,15 +4711,15 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="51" ht="40.5" spans="1:12">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -4670,7 +4734,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4685,12 +4749,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="52" ht="54" spans="1:12">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4708,7 +4772,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4723,12 +4787,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="53" ht="40.5" spans="1:12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="53" ht="54" spans="1:12">
       <c r="A53" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4746,7 +4810,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4761,12 +4825,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="54" ht="42" spans="1:12">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" ht="40.5" spans="1:12">
       <c r="A54" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4784,7 +4848,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4799,12 +4863,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="55" ht="57" spans="1:12">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="55" ht="42" spans="1:12">
       <c r="A55" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4822,7 +4886,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4837,12 +4901,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="56" ht="40.5" spans="1:12">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="56" ht="57" spans="1:12">
       <c r="A56" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4860,7 +4924,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4875,12 +4939,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="57" ht="54" spans="1:12">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4898,7 +4962,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4913,12 +4977,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="58" ht="67.5" spans="1:12">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="58" ht="54" spans="1:12">
       <c r="A58" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4936,7 +5000,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4951,15 +5015,15 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59" ht="67.5" spans="1:12">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
@@ -4974,7 +5038,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4989,15 +5053,15 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="60" ht="54" spans="1:12">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -5012,7 +5076,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5027,12 +5091,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5050,7 +5114,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5065,12 +5129,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="62" ht="30" spans="1:12">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="62" ht="54" spans="1:12">
       <c r="A62" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5088,7 +5152,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5100,13 +5164,13 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="L62" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="63" ht="54" spans="1:12">
+    <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
         <v>211</v>
       </c>
@@ -5137,14 +5201,14 @@
       <c r="J63" t="s">
         <v>15</v>
       </c>
-      <c r="K63" s="2" t="s">
+      <c r="K63" t="s">
         <v>213</v>
       </c>
       <c r="L63" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
         <v>215</v>
       </c>
@@ -5164,7 +5228,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>216</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5175,16 +5239,16 @@
       <c r="J64" t="s">
         <v>15</v>
       </c>
-      <c r="K64" t="s">
-        <v>15</v>
+      <c r="K64" s="3" t="s">
+        <v>217</v>
       </c>
       <c r="L64" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="65" ht="67.5" spans="1:12">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5202,7 +5266,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>217</v>
+        <v>15</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5217,12 +5281,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="66" ht="40.5" spans="1:12">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" ht="67.5" spans="1:12">
       <c r="A66" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5240,7 +5304,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5252,15 +5316,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>221</v>
+        <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>130</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5278,7 +5342,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5290,15 +5354,15 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>15</v>
+        <v>225</v>
       </c>
       <c r="L67" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="68" ht="45" spans="1:12">
+    <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5316,7 +5380,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5328,13 +5392,13 @@
         <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>226</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="69" ht="54" spans="1:12">
+        <v>15</v>
+      </c>
+      <c r="L68" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" ht="45" spans="1:12">
       <c r="A69" t="s">
         <v>228</v>
       </c>
@@ -5366,18 +5430,18 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>15</v>
-      </c>
-      <c r="L69" s="3" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="70" spans="1:12">
+      <c r="L69" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="70" ht="54" spans="1:12">
       <c r="A70" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5392,7 +5456,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5406,16 +5470,16 @@
       <c r="K70" t="s">
         <v>15</v>
       </c>
-      <c r="L70" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="71" ht="40.5" spans="1:12">
+      <c r="L70" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -5430,7 +5494,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5445,12 +5509,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="72" ht="67.5" spans="1:12">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5468,7 +5532,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5480,18 +5544,18 @@
         <v>15</v>
       </c>
       <c r="K72" t="s">
-        <v>238</v>
+        <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" ht="67.5" spans="1:12">
       <c r="A73" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B73" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -5506,7 +5570,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5518,57 +5582,57 @@
         <v>15</v>
       </c>
       <c r="K73" t="s">
-        <v>15</v>
+        <v>242</v>
       </c>
       <c r="L73" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="74" ht="27" spans="1:12">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B74" t="s">
+        <v>40</v>
+      </c>
+      <c r="C74" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" t="s">
+        <v>15</v>
+      </c>
+      <c r="E74" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" t="s">
+        <v>244</v>
+      </c>
+      <c r="H74" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" t="s">
+        <v>15</v>
+      </c>
+      <c r="J74" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" t="s">
+        <v>15</v>
+      </c>
+      <c r="L74" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="75" ht="27" spans="1:12">
+      <c r="A75" t="s">
+        <v>246</v>
+      </c>
+      <c r="B75" t="s">
         <v>13</v>
       </c>
-      <c r="C74" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E74" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" t="s">
-        <v>15</v>
-      </c>
-      <c r="G74" t="s">
-        <v>243</v>
-      </c>
-      <c r="H74" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" t="s">
-        <v>15</v>
-      </c>
-      <c r="J74" t="s">
-        <v>15</v>
-      </c>
-      <c r="K74" t="s">
-        <v>15</v>
-      </c>
-      <c r="L74" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12">
-      <c r="A75" t="s">
-        <v>245</v>
-      </c>
-      <c r="B75" t="s">
-        <v>29</v>
-      </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
@@ -5582,7 +5646,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5597,15 +5661,15 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="76" ht="40.5" spans="1:12">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5620,7 +5684,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5635,12 +5699,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="77" ht="40.5" spans="1:12">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5658,7 +5722,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5673,12 +5737,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="78" ht="54" spans="1:12">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5696,7 +5760,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5711,12 +5775,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="79" ht="40.5" spans="1:12">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="79" ht="54" spans="1:12">
       <c r="A79" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5734,7 +5798,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5749,12 +5813,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="80" ht="54" spans="1:12">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="80" ht="40.5" spans="1:12">
       <c r="A80" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5772,7 +5836,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5787,15 +5851,15 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" ht="54" spans="1:12">
       <c r="A81" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B81" t="s">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -5810,7 +5874,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5822,18 +5886,18 @@
         <v>15</v>
       </c>
       <c r="K81" t="s">
-        <v>156</v>
+        <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="82" ht="54" spans="1:12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -5848,7 +5912,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5860,15 +5924,15 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="L82" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="83" ht="40.5" spans="1:12">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="83" ht="54" spans="1:12">
       <c r="A83" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5886,7 +5950,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5901,12 +5965,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="84" ht="67.5" spans="1:12">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5924,7 +5988,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5939,12 +6003,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="85" ht="40.5" spans="1:12">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="85" ht="67.5" spans="1:12">
       <c r="A85" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -5962,7 +6026,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -5977,15 +6041,15 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B86" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
@@ -6000,7 +6064,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6015,15 +6079,15 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="87" ht="40.5" spans="1:12">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
@@ -6038,7 +6102,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6053,12 +6117,12 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>197</v>
+        <v>276</v>
       </c>
     </row>
     <row r="88" ht="40.5" spans="1:12">
       <c r="A88" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6076,7 +6140,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6091,12 +6155,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="89" ht="27" spans="1:12">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="89" ht="40.5" spans="1:12">
       <c r="A89" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6114,7 +6178,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6129,12 +6193,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="90" ht="69" spans="1:12">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="90" ht="27" spans="1:12">
       <c r="A90" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6152,7 +6216,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6167,12 +6231,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="91" ht="67.5" spans="1:12">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="91" ht="69" spans="1:12">
       <c r="A91" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6190,7 +6254,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6208,9 +6272,9 @@
         <v>210</v>
       </c>
     </row>
-    <row r="92" ht="54" spans="1:12">
+    <row r="92" ht="67.5" spans="1:12">
       <c r="A92" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6228,7 +6292,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6240,10 +6304,10 @@
         <v>15</v>
       </c>
       <c r="K92" t="s">
-        <v>286</v>
+        <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>287</v>
+        <v>214</v>
       </c>
     </row>
     <row r="93" ht="54" spans="1:12">
@@ -6278,15 +6342,15 @@
         <v>15</v>
       </c>
       <c r="K93" t="s">
-        <v>15</v>
+        <v>290</v>
       </c>
       <c r="L93" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="94" ht="54" spans="1:12">
       <c r="A94" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6304,7 +6368,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6315,24 +6379,26 @@
       <c r="J94" t="s">
         <v>15</v>
       </c>
-      <c r="K94" s="2" t="s">
-        <v>213</v>
+      <c r="K94" t="s">
+        <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="95" ht="90" spans="1:12">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B95" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
       </c>
-      <c r="D95"/>
+      <c r="D95" t="s">
+        <v>15</v>
+      </c>
       <c r="E95" t="s">
         <v>15</v>
       </c>
@@ -6340,7 +6406,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6351,22 +6417,23 @@
       <c r="J95" t="s">
         <v>15</v>
       </c>
-      <c r="K95"/>
+      <c r="K95" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="L95" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="96" ht="28.5" spans="1:12">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="96" ht="90" spans="1:12">
       <c r="A96" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
       </c>
-      <c r="D96"/>
       <c r="E96" t="s">
         <v>15</v>
       </c>
@@ -6374,7 +6441,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6385,14 +6452,13 @@
       <c r="J96" t="s">
         <v>15</v>
       </c>
-      <c r="K96"/>
       <c r="L96" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="97" ht="55.5" spans="1:12">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="97" ht="28.5" spans="1:12">
       <c r="A97" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6400,9 +6466,6 @@
       <c r="C97" t="s">
         <v>14</v>
       </c>
-      <c r="D97" t="s">
-        <v>15</v>
-      </c>
       <c r="E97" t="s">
         <v>15</v>
       </c>
@@ -6410,7 +6473,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6421,11 +6484,46 @@
       <c r="J97" t="s">
         <v>15</v>
       </c>
-      <c r="K97" t="s">
-        <v>301</v>
-      </c>
       <c r="L97" t="s">
-        <v>302</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" ht="55.5" spans="1:12">
+      <c r="A98" t="s">
+        <v>303</v>
+      </c>
+      <c r="B98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98" t="s">
+        <v>15</v>
+      </c>
+      <c r="E98" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" t="s">
+        <v>15</v>
+      </c>
+      <c r="G98" t="s">
+        <v>304</v>
+      </c>
+      <c r="H98" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" t="s">
+        <v>15</v>
+      </c>
+      <c r="J98" t="s">
+        <v>15</v>
+      </c>
+      <c r="K98" t="s">
+        <v>305</v>
+      </c>
+      <c r="L98" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -6446,39 +6544,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6486,82 +6584,82 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B11" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B12" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B13" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B14" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B15" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -6583,616 +6681,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B6" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C6" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D6" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E6" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B7" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C7" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D7" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E7" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F7" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B8" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C8" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D8" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F8" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B9" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C9" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D9" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="E9" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F9" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B10" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C10" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D10" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E10" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F10" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B11" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C11" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D11" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="E11" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="F11" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B12" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C12" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D12" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E12" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F12" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B13" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="C13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="D13" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="E13" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F13" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B14" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C14" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D14" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="E14" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F14" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B15" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C15" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D15" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E15" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F15" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B16" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C16" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D16" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E16" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F16" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B17" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C17" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D17" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E17" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F17" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B18" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="C18" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D18" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E18" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F18" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B19" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C19" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="D19" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E19" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F19" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B20" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C20" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D20" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E20" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F20" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B21" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C21" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D21" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E21" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F21" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B22" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C22" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D22" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E22" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F22" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B23" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C23" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D23" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E23" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F23" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B24" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C24" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D24" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E24" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F24" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B25" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C25" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D25" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E25" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F25" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B26" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C26" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D26" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E26" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="F26" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B27" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C27" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D27" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E27" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F27" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B28" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C28" t="s">
+        <v>466</v>
+      </c>
+      <c r="D28" t="s">
         <v>462</v>
       </c>
-      <c r="D28" t="s">
-        <v>458</v>
-      </c>
       <c r="E28" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F28" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B29" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C29" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D29" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E29" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F29" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="B30" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C30" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D30" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E30" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F30" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B31" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C31" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D31" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(4).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark3F(4).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线3层（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1374" uniqueCount="484">
   <si>
     <t>ID</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>false</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music22)</t>
   </si>
   <si>
     <t>源类型=type:exeBC; 层级=0</t>
@@ -2917,18 +2920,18 @@
         <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="90" spans="1:12">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -2943,7 +2946,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
@@ -2958,12 +2961,12 @@
         <v>15</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="42" spans="1:12">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2981,7 +2984,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2996,12 +2999,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="40.5" spans="1:12">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -3019,7 +3022,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -3034,15 +3037,15 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="42" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -3054,7 +3057,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -3066,12 +3069,12 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -3086,7 +3089,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -3098,12 +3101,12 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="54" spans="1:12">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -3121,7 +3124,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -3136,21 +3139,21 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="30" spans="1:12">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>15</v>
@@ -3159,7 +3162,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -3171,24 +3174,24 @@
         <v>15</v>
       </c>
       <c r="K9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" ht="54" spans="1:12">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -3197,7 +3200,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -3212,21 +3215,21 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="30" spans="1:12">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -3235,7 +3238,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -3247,15 +3250,15 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -3273,7 +3276,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3288,21 +3291,21 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="55.5" spans="1:12">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3311,7 +3314,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3323,15 +3326,15 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" ht="40.5" spans="1:12">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3340,7 +3343,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3349,7 +3352,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3361,15 +3364,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" ht="54" spans="1:12">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3387,7 +3390,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3402,21 +3405,21 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="40.5" spans="1:12">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3425,7 +3428,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3437,24 +3440,24 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" ht="72" spans="1:12">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3463,7 +3466,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3478,21 +3481,21 @@
         <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="30" spans="1:12">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
         <v>15</v>
@@ -3501,7 +3504,7 @@
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H18" t="s">
         <v>15</v>
@@ -3516,12 +3519,12 @@
         <v>15</v>
       </c>
       <c r="L18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" ht="30" spans="1:12">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3530,7 +3533,7 @@
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E19" t="s">
         <v>15</v>
@@ -3539,22 +3542,22 @@
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s">
         <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
       </c>
       <c r="K19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" ht="67.5" spans="1:12">
@@ -3568,24 +3571,24 @@
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:12">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3594,7 +3597,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3606,24 +3609,24 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="30" spans="1:12">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3632,7 +3635,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3644,15 +3647,15 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" ht="54" spans="1:12">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3670,7 +3673,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3682,24 +3685,24 @@
         <v>15</v>
       </c>
       <c r="K23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" ht="30" spans="1:12">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
         <v>15</v>
@@ -3708,7 +3711,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3720,15 +3723,15 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L24" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" ht="54" spans="1:12">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3737,7 +3740,7 @@
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -3746,7 +3749,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3761,21 +3764,21 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="30" spans="1:12">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3784,7 +3787,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3799,21 +3802,21 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:12">
       <c r="A27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3822,7 +3825,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3834,15 +3837,15 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" ht="40.5" spans="1:12">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3860,7 +3863,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3875,21 +3878,21 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" ht="30" spans="1:12">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E29" t="s">
         <v>15</v>
@@ -3898,7 +3901,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3910,24 +3913,24 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" ht="30" spans="1:12">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E30" t="s">
         <v>15</v>
@@ -3936,7 +3939,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3951,12 +3954,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" ht="55.5" spans="1:12">
       <c r="A31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3965,7 +3968,7 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E31" t="s">
         <v>15</v>
@@ -3974,7 +3977,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3986,15 +3989,15 @@
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4012,7 +4015,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4027,12 +4030,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4050,7 +4053,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4065,12 +4068,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" ht="27" spans="1:12">
       <c r="A34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4088,7 +4091,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4103,12 +4106,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" ht="45" spans="1:12">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4138,15 +4141,15 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4179,12 +4182,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" ht="40.5" spans="1:12">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4202,7 +4205,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4217,12 +4220,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4240,7 +4243,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4255,12 +4258,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" ht="40.5" spans="1:12">
       <c r="A39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4278,7 +4281,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4290,15 +4293,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4316,7 +4319,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4331,12 +4334,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="41" ht="55.5" spans="1:12">
       <c r="A41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4354,7 +4357,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4369,12 +4372,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="42" ht="40.5" spans="1:12">
       <c r="A42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4392,7 +4395,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4407,12 +4410,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4430,7 +4433,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4445,12 +4448,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" ht="55.5" spans="1:12">
       <c r="A44" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4468,7 +4471,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4483,12 +4486,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" ht="55.5" spans="1:12">
       <c r="A45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4506,7 +4509,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4521,15 +4524,15 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -4544,7 +4547,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4556,15 +4559,15 @@
         <v>15</v>
       </c>
       <c r="K46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" ht="54" spans="1:12">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4582,7 +4585,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4594,15 +4597,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4620,7 +4623,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4635,12 +4638,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" ht="67.5" spans="1:12">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4658,7 +4661,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4673,12 +4676,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4696,7 +4699,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4711,15 +4714,15 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
@@ -4734,7 +4737,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4749,12 +4752,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4772,7 +4775,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4787,12 +4790,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" ht="54" spans="1:12">
       <c r="A53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4810,7 +4813,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4825,12 +4828,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" ht="40.5" spans="1:12">
       <c r="A54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4848,7 +4851,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4863,12 +4866,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" ht="42" spans="1:12">
       <c r="A55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4886,7 +4889,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4901,12 +4904,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" ht="57" spans="1:12">
       <c r="A56" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4924,7 +4927,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4939,12 +4942,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4962,7 +4965,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4977,12 +4980,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" ht="54" spans="1:12">
       <c r="A58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5000,7 +5003,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5015,12 +5018,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" ht="67.5" spans="1:12">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5038,7 +5041,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5053,15 +5056,15 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -5076,7 +5079,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5091,12 +5094,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" ht="54" spans="1:12">
       <c r="A61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5114,7 +5117,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5129,12 +5132,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" ht="54" spans="1:12">
       <c r="A62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5152,7 +5155,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5167,12 +5170,12 @@
         <v>15</v>
       </c>
       <c r="L62" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" ht="30" spans="1:12">
       <c r="A63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5190,7 +5193,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5202,15 +5205,15 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L63" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5228,7 +5231,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5240,15 +5243,15 @@
         <v>15</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L64" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5281,12 +5284,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" ht="67.5" spans="1:12">
       <c r="A66" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5304,7 +5307,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5319,12 +5322,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5342,7 +5345,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5354,15 +5357,15 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L67" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5380,7 +5383,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5395,12 +5398,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69" ht="45" spans="1:12">
       <c r="A69" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -5418,7 +5421,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5430,15 +5433,15 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" ht="54" spans="1:12">
       <c r="A70" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5456,7 +5459,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5471,15 +5474,15 @@
         <v>15</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C71" t="s">
         <v>14</v>
@@ -5494,7 +5497,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5509,12 +5512,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72" ht="40.5" spans="1:12">
       <c r="A72" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5532,7 +5535,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5547,12 +5550,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73" ht="67.5" spans="1:12">
       <c r="A73" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5570,7 +5573,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5582,18 +5585,18 @@
         <v>15</v>
       </c>
       <c r="K73" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L73" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B74" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -5608,7 +5611,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5623,12 +5626,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="75" ht="27" spans="1:12">
       <c r="A75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5646,7 +5649,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5661,15 +5664,15 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5684,7 +5687,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5699,12 +5702,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" ht="40.5" spans="1:12">
       <c r="A77" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5722,7 +5725,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5737,12 +5740,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5760,7 +5763,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5775,12 +5778,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" ht="54" spans="1:12">
       <c r="A79" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5798,7 +5801,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5813,12 +5816,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" ht="40.5" spans="1:12">
       <c r="A80" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5836,7 +5839,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5851,12 +5854,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="81" ht="54" spans="1:12">
       <c r="A81" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B81" t="s">
         <v>13</v>
@@ -5874,7 +5877,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5889,15 +5892,15 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B82" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -5912,7 +5915,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5924,15 +5927,15 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L82" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="83" ht="54" spans="1:12">
       <c r="A83" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -5950,7 +5953,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5965,12 +5968,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5988,7 +5991,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6003,12 +6006,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="85" ht="67.5" spans="1:12">
       <c r="A85" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6026,7 +6029,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6041,12 +6044,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6064,7 +6067,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6079,15 +6082,15 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
@@ -6102,7 +6105,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6117,12 +6120,12 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="88" ht="40.5" spans="1:12">
       <c r="A88" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6140,7 +6143,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6155,12 +6158,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="89" ht="40.5" spans="1:12">
       <c r="A89" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6178,7 +6181,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6193,12 +6196,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="90" ht="27" spans="1:12">
       <c r="A90" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6216,7 +6219,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6231,12 +6234,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="91" ht="69" spans="1:12">
       <c r="A91" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6254,7 +6257,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6269,12 +6272,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="92" ht="67.5" spans="1:12">
       <c r="A92" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6292,7 +6295,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6307,12 +6310,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="93" ht="54" spans="1:12">
       <c r="A93" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6330,7 +6333,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6342,15 +6345,15 @@
         <v>15</v>
       </c>
       <c r="K93" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L93" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="94" ht="54" spans="1:12">
       <c r="A94" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6368,7 +6371,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6383,12 +6386,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6406,7 +6409,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6418,18 +6421,18 @@
         <v>15</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L95" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="96" ht="90" spans="1:12">
       <c r="A96" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
@@ -6441,7 +6444,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6453,12 +6456,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="97" ht="28.5" spans="1:12">
       <c r="A97" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6473,7 +6476,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6485,12 +6488,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98" ht="55.5" spans="1:12">
       <c r="A98" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6508,7 +6511,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6520,10 +6523,10 @@
         <v>15</v>
       </c>
       <c r="K98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L98" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -6544,39 +6547,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -6584,82 +6587,82 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B12" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -6681,616 +6684,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D5" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B12" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C12" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D12" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F12" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C13" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D13" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E13" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F13" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B15" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C15" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D15" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E15" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C16" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D16" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F16" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C17" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D17" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E17" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F17" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B18" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C18" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E18" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B19" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C19" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E20" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F20" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B21" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C21" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D21" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F21" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B22" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C22" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D22" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E22" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F22" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B23" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C23" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E23" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F23" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B24" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C24" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D24" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E24" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F24" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B25" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C25" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D25" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F25" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B26" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C26" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D26" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F26" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B27" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D27" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F27" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B28" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C28" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D28" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E28" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F28" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B29" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C29" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D29" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F29" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B30" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C30" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D30" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E30" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F30" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B31" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C31" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D31" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
